--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA298"/>
+  <dimension ref="A1:AA306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32205,6 +32205,878 @@
       <c r="Z298" s="2" t="inlineStr"/>
       <c r="AA298" s="2" t="inlineStr"/>
     </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>Max Badri-Hollander</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-badri-hollander-7399ab151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Mehrtens</t>
+        </is>
+      </c>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; eCommerce Manager</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgia-mehrtens-6b0682291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr"/>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr">
+        <is>
+          <t>Angel Faye Gabisan</t>
+        </is>
+      </c>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angelgabisan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>Will Brunel-Morvan</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>National Trade Manager</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/will-brunel-morvan-59543034/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr"/>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr">
+        <is>
+          <t>Tim Ippel</t>
+        </is>
+      </c>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>Trade Representative</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timippel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr">
+        <is>
+          <t>Scott Hurrell</t>
+        </is>
+      </c>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-hurrell-64149554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr"/>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr">
+        <is>
+          <t>Bertrand Soalhat</t>
+        </is>
+      </c>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertrand-soalhat-8814a711b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr">
+        <is>
+          <t>Scott Gray</t>
+        </is>
+      </c>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-gray-06436960/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA306"/>
+  <dimension ref="A1:AA314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33077,6 +33077,878 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>Max Badri-Hollander</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-badri-hollander-7399ab151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Mehrtens</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; eCommerce Manager</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgia-mehrtens-6b0682291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr"/>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr">
+        <is>
+          <t>Angel Faye Gabisan</t>
+        </is>
+      </c>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angelgabisan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>Will Brunel-Morvan</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>National Trade Manager</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/will-brunel-morvan-59543034/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr"/>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr">
+        <is>
+          <t>Tim Ippel</t>
+        </is>
+      </c>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>Trade Representative</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timippel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr">
+        <is>
+          <t>Scott Hurrell</t>
+        </is>
+      </c>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-hurrell-64149554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>Bertrand Soalhat</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertrand-soalhat-8814a711b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>Scott Gray</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-gray-06436960/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA314"/>
+  <dimension ref="A1:AA327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33949,6 +33949,1391 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Progressive Trading</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr"/>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>168867</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr"/>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>15 Oak Road</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.progressivetrading.co.nz</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr"/>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>admin@progressivetrading.net</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>+64 9 636 6999</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr"/>
+      <c r="Q315" s="2" t="inlineStr"/>
+      <c r="R315" s="2" t="inlineStr"/>
+      <c r="S315" s="2" t="inlineStr"/>
+      <c r="T315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr"/>
+      <c r="X315" s="2" t="inlineStr"/>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr"/>
+      <c r="AA315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>Jashon Yumnam</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr"/>
+      <c r="AA316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jashon-yumnam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>Martyn Norris</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>Category Manager</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="AA317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martyn-norris-bb086189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>Ryan Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr"/>
+      <c r="AA318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryan-fitzpatrick-a4a204202/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Sapori D'italia Import Limited</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Sapori D'italia Import Limited</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>10839</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Kumeū</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>133 Puke Road</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>0891</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>info@sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>+64 9 848 4269</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>4618185</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr"/>
+      <c r="S319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/saporiditalia/</t>
+        </is>
+      </c>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@saporiditalia4176</t>
+        </is>
+      </c>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>Marco Nordio</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/pub/marco-nordio/1a/a1a/256/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>Max Badri-Hollander</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-badri-hollander-7399ab151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Mehrtens</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; eCommerce Manager</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgia-mehrtens-6b0682291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>Angel Faye Gabisan</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr"/>
+      <c r="AA322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angelgabisan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>Will Brunel-Morvan</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>National Trade Manager</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/will-brunel-morvan-59543034/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>Tim Ippel</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>Trade Representative</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timippel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>Scott Hurrell</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-hurrell-64149554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>Bertrand Soalhat</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertrand-soalhat-8814a711b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>Scott Gray</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-gray-06436960/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA327"/>
+  <dimension ref="A1:AA340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35334,6 +35334,1419 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Del Mundo Limited</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Del Mundo Limited</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>122628</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Ground Floor, ANZAC House 181 Willis Street</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://delmundo.co.nz</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>info@delmundo.co.nz</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr"/>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>6273567</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr"/>
+      <c r="S328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delmundo.co.nz/</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Monge</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucas-monge-3a6411243</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>Jashon Yumnam</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jashon-yumnam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>Martyn Norris</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>Category Manager</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martyn-norris-bb086189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Gilmours Wholesale Limited</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>80448</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>37 Constellation Drive</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>0632</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>orders@gilmours.co.nz</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>+64 800 270 414</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>2356569</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gilmours-nz/</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gilmourswholesale</t>
+        </is>
+      </c>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gilmoursnz/</t>
+        </is>
+      </c>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdKHPU3jo68optJ2YymyvKA/featured</t>
+        </is>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>Ryan Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryan-fitzpatrick-a4a204202/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Sapori D'italia Import Limited</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Sapori D'italia Import Limited</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>10839</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Kumeū</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>133 Puke Road</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>0891</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>info@sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>+64 9 848 4269</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>4618185</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/saporiditalia/</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sapori.co.nz</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@saporiditalia4176</t>
+        </is>
+      </c>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Marco Nordio</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr"/>
+      <c r="AA332" s="2" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/pub/marco-nordio/1a/a1a/256/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Max Badri-Hollander</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr"/>
+      <c r="AA333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-badri-hollander-7399ab151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Mehrtens</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; eCommerce Manager</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr"/>
+      <c r="AA334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgia-mehrtens-6b0682291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Angel Faye Gabisan</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angelgabisan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Will Brunel-Morvan</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>National Trade Manager</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/will-brunel-morvan-59543034/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Tim Ippel</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>Trade Representative</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timippel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Scott Hurrell</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-hurrell-64149554/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Bertrand Soalhat</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Trade Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertrand-soalhat-8814a711b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron Limited</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Maison Vauron</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>10828</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>5 McColl Street</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>sales@mvauron.co.nz</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+64 9-529 0157</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>961624</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maisonvauron/</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maisonvauron</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Scott Gray</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-gray-06436960/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
